--- a/KS_year1_awardees.xlsx
+++ b/KS_year1_awardees.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t xml:space="preserve">Read this before using any figure</t>
   </si>
@@ -73,7 +73,7 @@
     <t xml:space="preserve">THE HOSPITAL FIGURE IS A FLOOR: $35,721,277 across 21 named hospitals.</t>
   </si>
   <si>
-    <t xml:space="preserve">A FURTHER 22 ROWS, $39,249,763, ARE NAMED RECIPIENTS WHOSE FORM KDHE</t>
+    <t xml:space="preserve">A FURTHER 23 ROWS, $40,182,073, ARE NAMED RECIPIENTS WHOSE FORM KDHE</t>
   </si>
   <si>
     <t xml:space="preserve">NOWHERE STATES -- more money than the confirmed figure. They are coded</t>
@@ -404,21 +404,6 @@
   </si>
   <si>
     <t xml:space="preserve">Salina Regional Health Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unclear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KDHE RPGP award. Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 PASS_THROUGH_UNRESOLVED: the recipient is not a hospital, and the source states that funds reach hospitals it does not name. §0.3 -- eligibility is not receipt -- so this is not imputed to Yes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PASS_THROUGH_UNRESOLVED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recipient is named but the source does not state its organisational form; §8 settled fallback (session 10). §10.2 PASS_THROUGH_UNRESOLVED: the recipient is not a hospital, and the source states that funds reach hospitals it does not name. §0.3 -- eligibility is not receipt -- so this is not imputed to Yes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELIGIBILITY_NOT_RECEIPT</t>
   </si>
   <si>
     <t xml:space="preserve">Mercy Hospital Pittsburg</t>
@@ -3696,10 +3681,10 @@
         <v>84</v>
       </c>
       <c r="F36" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="G36" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="H36" t="s">
         <v>58</v>
@@ -3733,7 +3718,7 @@
         <v>105</v>
       </c>
       <c r="U36" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="V36" t="s">
         <v>58</v>
@@ -3745,13 +3730,13 @@
         <v>89</v>
       </c>
       <c r="Y36" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="Z36" t="s">
         <v>91</v>
       </c>
       <c r="AA36" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="AB36" t="s">
         <v>72</v>
@@ -3765,7 +3750,7 @@
         <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D37" t="n">
         <v>681711</v>
@@ -3841,7 +3826,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D38" t="n">
         <v>677248</v>
@@ -3917,7 +3902,7 @@
         <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D39" t="n">
         <v>196650</v>
@@ -3995,7 +3980,7 @@
         <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D40" t="n">
         <v>173355</v>
@@ -4073,7 +4058,7 @@
         <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D41" t="n">
         <v>150000</v>
@@ -4085,7 +4070,7 @@
         <v>58</v>
       </c>
       <c r="G41" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H41" t="s">
         <v>58</v>
@@ -4097,7 +4082,7 @@
         <v>60</v>
       </c>
       <c r="K41" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s">
         <v>62</v>
@@ -4116,7 +4101,7 @@
       <c r="R41"/>
       <c r="S41"/>
       <c r="T41" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="U41" t="s">
         <v>67</v>
@@ -4138,7 +4123,7 @@
       </c>
       <c r="AA41"/>
       <c r="AB41" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42">
@@ -4149,7 +4134,7 @@
         <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D42" t="n">
         <v>150000</v>
@@ -4161,7 +4146,7 @@
         <v>58</v>
       </c>
       <c r="G42" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H42" t="s">
         <v>58</v>
@@ -4173,7 +4158,7 @@
         <v>60</v>
       </c>
       <c r="K42" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L42" t="s">
         <v>62</v>
@@ -4192,7 +4177,7 @@
       <c r="R42"/>
       <c r="S42"/>
       <c r="T42" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="U42" t="s">
         <v>67</v>
@@ -4214,7 +4199,7 @@
       </c>
       <c r="AA42"/>
       <c r="AB42" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43">
@@ -4225,7 +4210,7 @@
         <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D43" t="n">
         <v>150000</v>
@@ -4237,7 +4222,7 @@
         <v>85</v>
       </c>
       <c r="G43" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H43" t="s">
         <v>58</v>
@@ -4249,7 +4234,7 @@
         <v>60</v>
       </c>
       <c r="K43" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L43" t="s">
         <v>62</v>
@@ -4268,7 +4253,7 @@
       <c r="R43"/>
       <c r="S43"/>
       <c r="T43" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="U43" t="s">
         <v>87</v>
@@ -4292,7 +4277,7 @@
         <v>92</v>
       </c>
       <c r="AB43" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44">
@@ -4303,7 +4288,7 @@
         <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D44" t="n">
         <v>150000</v>
@@ -4315,7 +4300,7 @@
         <v>58</v>
       </c>
       <c r="G44" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H44" t="s">
         <v>58</v>
@@ -4327,7 +4312,7 @@
         <v>60</v>
       </c>
       <c r="K44" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L44" t="s">
         <v>62</v>
@@ -4346,7 +4331,7 @@
       <c r="R44"/>
       <c r="S44"/>
       <c r="T44" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="U44" t="s">
         <v>67</v>
@@ -4368,7 +4353,7 @@
       </c>
       <c r="AA44"/>
       <c r="AB44" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45">
@@ -4379,7 +4364,7 @@
         <v>44</v>
       </c>
       <c r="C45" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D45" t="n">
         <v>149960</v>
@@ -4391,7 +4376,7 @@
         <v>85</v>
       </c>
       <c r="G45" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H45" t="s">
         <v>58</v>
@@ -4403,7 +4388,7 @@
         <v>60</v>
       </c>
       <c r="K45" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L45" t="s">
         <v>62</v>
@@ -4422,7 +4407,7 @@
       <c r="R45"/>
       <c r="S45"/>
       <c r="T45" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="U45" t="s">
         <v>87</v>
@@ -4446,7 +4431,7 @@
         <v>92</v>
       </c>
       <c r="AB45" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="46">
@@ -4457,7 +4442,7 @@
         <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D46" t="n">
         <v>146476</v>
@@ -4469,7 +4454,7 @@
         <v>85</v>
       </c>
       <c r="G46" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H46" t="s">
         <v>58</v>
@@ -4481,7 +4466,7 @@
         <v>60</v>
       </c>
       <c r="K46" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L46" t="s">
         <v>62</v>
@@ -4500,7 +4485,7 @@
       <c r="R46"/>
       <c r="S46"/>
       <c r="T46" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="U46" t="s">
         <v>87</v>
@@ -4524,7 +4509,7 @@
         <v>92</v>
       </c>
       <c r="AB46" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47">
@@ -4535,7 +4520,7 @@
         <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D47" t="n">
         <v>110716</v>
@@ -4547,7 +4532,7 @@
         <v>58</v>
       </c>
       <c r="G47" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H47" t="s">
         <v>58</v>
@@ -4559,7 +4544,7 @@
         <v>60</v>
       </c>
       <c r="K47" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s">
         <v>62</v>
@@ -4578,7 +4563,7 @@
       <c r="R47"/>
       <c r="S47"/>
       <c r="T47" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="U47" t="s">
         <v>67</v>
@@ -4600,7 +4585,7 @@
       </c>
       <c r="AA47"/>
       <c r="AB47" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -4619,15 +4604,15 @@
         <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B2" t="n">
         <v>7</v>
